--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13188_Strict_comparison_operators.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-13188_Strict_comparison_operators.xlsx
@@ -2,16 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet state="visible" name="Double" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="136">
   <si>
     <t>// ( ==== ) Strict equality operator checks if the values of two operands are equal or not without considering inaccuracy of float point values. If values are equal strictly then condition becomes true</t>
   </si>
@@ -281,12 +283,151 @@
   </si>
   <si>
     <t>Test DoubleDivision</t>
+  </si>
+  <si>
+    <t>// Double arithmetic computes with the decimals the numbers show, but a quotient without a finite decimal is rounded to a Double. The next tests will be compared result for different double types: 'd, Double, double'</t>
+  </si>
+  <si>
+    <t>// In the DoubleAddition case in OpenL result will be ( 0.9999999999999999 ) instead 1</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== ( 0.9999999999999999 ) and !=== 1</t>
+  </si>
+  <si>
+    <t>// In the DoubleSubtraction case in OpenL result will be ( 0.7933333333333334 ) instead 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== ( 0.7933333333333334 ) and !=== 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>// In the DoubleMultiplication case in OpenL result will be ( 0.9999999999999999 ) instead 1</t>
+  </si>
+  <si>
+    <t>// In the DoubleDivision case in OpenL result will be ( 3.0000000000000004 ) instead 3</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== ( 3.0000000000000004 ) and !=== 3</t>
+  </si>
+  <si>
+    <t>= 1d / 3d + 2d / 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / (Double) 3 + (Double) 2 / (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 1 / (double) 3 + (double) 2 / (double) 3</t>
+  </si>
+  <si>
+    <t>= 1d</t>
+  </si>
+  <si>
+    <t>= (Double) 1</t>
+  </si>
+  <si>
+    <t>= (double) 1</t>
+  </si>
+  <si>
+    <t>= 0.9999999999999999d</t>
+  </si>
+  <si>
+    <t>= (Double) 0.9999999999999999</t>
+  </si>
+  <si>
+    <t>= (double) 0.9999999999999999</t>
+  </si>
+  <si>
+    <t>= 5d / 6d - 0.04d</t>
+  </si>
+  <si>
+    <t>= (Double) 5 / (Double) 6 - (Double) 0.04</t>
+  </si>
+  <si>
+    <t>= (double) 5 / (double) 6 - (double) 0.04</t>
+  </si>
+  <si>
+    <t>= 0.7933333333333333d</t>
+  </si>
+  <si>
+    <t>= (Double) 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>= (double) 0.7933333333333333</t>
+  </si>
+  <si>
+    <t>= 0.7933333333333334d</t>
+  </si>
+  <si>
+    <t>= (Double) 0.7933333333333334</t>
+  </si>
+  <si>
+    <t>= (double) 0.7933333333333334</t>
+  </si>
+  <si>
+    <t>= 1d / 3d * 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / (Double) 3 * (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 1 / (double) 3 * (double) 3</t>
+  </si>
+  <si>
+    <t>= 1d / (1d / 3d)</t>
+  </si>
+  <si>
+    <t>= (Double) 1 / ((Double) 1 / (Double) 3)</t>
+  </si>
+  <si>
+    <t>= (double) 1 / ((double) 1 / (double) 3)</t>
+  </si>
+  <si>
+    <t>= 3d</t>
+  </si>
+  <si>
+    <t>= (Double) 3</t>
+  </si>
+  <si>
+    <t>= (double) 3</t>
+  </si>
+  <si>
+    <t>= 3.0000000000000004d</t>
+  </si>
+  <si>
+    <t>= (Double) 3.0000000000000004</t>
+  </si>
+  <si>
+    <t>= (double) 3.0000000000000004</t>
+  </si>
+  <si>
+    <t>// Double arithmetic computes with the decimals the numbers show, and a computed number of 16 or 17 digits, such as a quotient, counts as its Double. The next tests will be compared result for different double types: 'd, Double, double'</t>
+  </si>
+  <si>
+    <t>// In the DoubleAddition case in OpenL result will be ( 1 ): 1/3 and 2/3 count as their Doubles, whose sum rounds to 1</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== 1 and !=== ( 0.9999999999999999 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleSubtraction case in OpenL result will be ( 0.7933333333333333 ): 5/6 counts as its Double and 0.04 as the decimal it shows</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== 0.7933333333333333 and !=== ( 0.7933333333333334 )</t>
+  </si>
+  <si>
+    <t>// In the DoubleMultiplication case in OpenL result will be ( 1 ): 1/3 counts as its Double</t>
+  </si>
+  <si>
+    <t>// In the DoubleDivision case in OpenL result will be ( 3 ): 1/3 counts as its Double</t>
+  </si>
+  <si>
+    <t>// The test below will be checked that 'case1' result ==== 3 and !=== ( 3.0000000000000004 )</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <sz val="10.0"/>
@@ -644,19 +785,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
+  <dimension ref="B1:N84"/>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="32.0"/>
-    <col customWidth="1" min="4" max="4" width="29.88"/>
-    <col customWidth="1" min="5" max="5" width="28.63"/>
-    <col customWidth="1" min="6" max="6" width="22.63"/>
-    <col customWidth="1" min="7" max="8" width="28.88"/>
-    <col customWidth="1" min="9" max="9" width="28.38"/>
-    <col customWidth="1" min="10" max="10" width="29.38"/>
-    <col customWidth="1" min="11" max="11" width="29.63"/>
-    <col customWidth="1" min="12" max="12" width="29.0"/>
-    <col customWidth="1" min="13" max="13" width="29.75"/>
-    <col customWidth="1" min="14" max="14" width="29.13"/>
+    <col min="3" max="3" customWidth="true" width="32.0"/>
+    <col min="4" max="4" customWidth="true" width="29.88"/>
+    <col min="5" max="5" customWidth="true" width="28.63"/>
+    <col min="6" max="6" customWidth="true" width="22.63"/>
+    <col min="7" max="8" customWidth="true" width="28.88"/>
+    <col min="9" max="9" customWidth="true" width="28.38"/>
+    <col min="10" max="10" customWidth="true" width="29.38"/>
+    <col min="11" max="11" customWidth="true" width="29.63"/>
+    <col min="12" max="12" customWidth="true" width="29.0"/>
+    <col min="13" max="13" customWidth="true" width="29.75"/>
+    <col min="14" max="14" customWidth="true" width="29.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -674,7 +816,7 @@
     </row>
     <row r="4">
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -687,12 +829,12 @@
     </row>
     <row r="7">
       <c r="B7" s="2" t="s">
-        <v>4</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -722,13 +864,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -736,13 +878,13 @@
         <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -750,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
@@ -917,40 +1059,40 @@
         <v>47</v>
       </c>
       <c r="C24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -960,12 +1102,12 @@
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30">
@@ -995,13 +1137,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33">
@@ -1009,13 +1151,13 @@
         <v>15</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
@@ -1023,13 +1165,13 @@
         <v>19</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
@@ -1190,40 +1332,40 @@
         <v>47</v>
       </c>
       <c r="C44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1233,12 +1375,12 @@
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
@@ -1268,13 +1410,13 @@
         <v>11</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53">
@@ -1282,13 +1424,13 @@
         <v>15</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54">
@@ -1296,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55">
@@ -1463,40 +1605,40 @@
         <v>47</v>
       </c>
       <c r="C64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -1506,12 +1648,12 @@
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70">
@@ -1541,13 +1683,13 @@
         <v>11</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73">
@@ -1555,13 +1697,13 @@
         <v>15</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74">
@@ -1569,13 +1711,13 @@
         <v>19</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75">
@@ -1736,40 +1878,40 @@
         <v>47</v>
       </c>
       <c r="C84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N84" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
